--- a/Document/課題一覧表.xlsx
+++ b/Document/課題一覧表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3E648A-D1D4-4F68-94FC-FFB6D6763D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39157756-BBD3-41DC-9079-ECF73920C4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
+    <workbookView xWindow="5415" yWindow="2445" windowWidth="28170" windowHeight="14655" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
   </bookViews>
   <sheets>
     <sheet name="課題一覧" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>課題一覧</t>
     <rPh sb="0" eb="2">
@@ -123,16 +123,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>動作確認・テスト実施</t>
-    <rPh sb="0" eb="4">
-      <t>ドウサカクニン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ジッシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>リリース</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -193,6 +183,39 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>ビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>動作確認・テスト実施
+余裕があるならテスト項目を作る</t>
+    <rPh sb="0" eb="4">
+      <t>ドウサカクニン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヨユウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カスタムコントロール非活性時の色</t>
+    <rPh sb="10" eb="13">
+      <t>ヒカッセイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>イロ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -218,12 +241,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -240,11 +269,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -269,8 +307,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}" name="テーブル1" displayName="テーブル1" ref="B5:F13" totalsRowShown="0">
-  <autoFilter ref="B5:F13" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}" name="テーブル1" displayName="テーブル1" ref="B5:F14" totalsRowShown="0">
+  <autoFilter ref="B5:F14" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}"/>
   <tableColumns count="5">
     <tableColumn id="2" xr3:uid="{A1D0E563-6C65-4A27-9D8B-5EE342B7CB85}" name="工程"/>
     <tableColumn id="3" xr3:uid="{D6C44085-30F4-400F-835B-6B497DB97442}" name="対応内容"/>
@@ -599,20 +637,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F429D69-C828-4F44-A95A-41969681F165}">
-  <dimension ref="B3:F13"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <dimension ref="B3:F14"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="48.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="3" max="3" width="48.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -620,16 +659,16 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -639,11 +678,14 @@
       <c r="D6" s="1">
         <v>46158</v>
       </c>
+      <c r="E6" s="1">
+        <v>46171</v>
+      </c>
       <c r="F6" s="1">
         <v>46173</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
         <v>4</v>
       </c>
@@ -660,27 +702,27 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B8" t="s">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4">
         <v>46158</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1">
+      <c r="E8" s="4"/>
+      <c r="F8" s="4">
         <v>46173</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1">
         <v>46158</v>
@@ -690,7 +732,7 @@
         <v>46186</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
         <v>7</v>
       </c>
@@ -704,45 +746,59 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="1">
+        <v>46171</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
         <v>9</v>
       </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="1">
-        <v>46158</v>
-      </c>
-      <c r="F11" s="1">
-        <v>46214</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
+      <c r="C12" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D12" s="1">
         <v>46158</v>
       </c>
       <c r="F12" s="1">
-        <v>46264</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.45">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
         <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
       </c>
       <c r="D13" s="1">
         <v>46158</v>
       </c>
       <c r="F13" s="1">
+        <v>46264</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1">
+        <v>46158</v>
+      </c>
+      <c r="F14" s="1">
         <v>46292</v>
       </c>
     </row>

--- a/Document/課題一覧表.xlsx
+++ b/Document/課題一覧表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39157756-BBD3-41DC-9079-ECF73920C4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8C8933-98B6-4A82-A9E6-0197740AF803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="2445" windowWidth="28170" windowHeight="14655" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
   </bookViews>
   <sheets>
     <sheet name="課題一覧" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>課題一覧</t>
     <rPh sb="0" eb="2">
@@ -216,6 +216,20 @@
     </rPh>
     <rPh sb="15" eb="16">
       <t>イロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>訂正モードの実装
+時間があれば</t>
+    <rPh sb="0" eb="2">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジカン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -307,8 +321,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}" name="テーブル1" displayName="テーブル1" ref="B5:F14" totalsRowShown="0">
-  <autoFilter ref="B5:F14" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}" name="テーブル1" displayName="テーブル1" ref="B5:F15" totalsRowShown="0">
+  <autoFilter ref="B5:F15" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}"/>
   <tableColumns count="5">
     <tableColumn id="2" xr3:uid="{A1D0E563-6C65-4A27-9D8B-5EE342B7CB85}" name="工程"/>
     <tableColumn id="3" xr3:uid="{D6C44085-30F4-400F-835B-6B497DB97442}" name="対応内容"/>
@@ -637,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F429D69-C828-4F44-A95A-41969681F165}">
-  <dimension ref="B3:F14"/>
+  <dimension ref="B3:F15"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
@@ -727,7 +741,9 @@
       <c r="D9" s="1">
         <v>46158</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="1">
+        <v>46172</v>
+      </c>
       <c r="F9" s="1">
         <v>46186</v>
       </c>
@@ -742,50 +758,54 @@
       <c r="D10" s="1">
         <v>46158</v>
       </c>
+      <c r="E10" s="1">
+        <v>46172</v>
+      </c>
       <c r="F10" s="1">
         <v>46201</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
         <v>7</v>
       </c>
-      <c r="C11" t="s">
-        <v>18</v>
+      <c r="C11" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D11" s="1">
-        <v>46171</v>
-      </c>
+        <v>46172</v>
+      </c>
+      <c r="E11" s="1"/>
       <c r="F11" s="1">
         <v>46201</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="1">
+        <v>46171</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D12" s="1">
-        <v>46158</v>
-      </c>
-      <c r="F12" s="1">
-        <v>46214</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>11</v>
       </c>
       <c r="D13" s="1">
         <v>46158</v>
       </c>
       <c r="F13" s="1">
-        <v>46264</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.4">
@@ -793,12 +813,26 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" s="1">
         <v>46158</v>
       </c>
       <c r="F14" s="1">
+        <v>46264</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46158</v>
+      </c>
+      <c r="F15" s="1">
         <v>46292</v>
       </c>
     </row>

--- a/Document/課題一覧表.xlsx
+++ b/Document/課題一覧表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8C8933-98B6-4A82-A9E6-0197740AF803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7D9379-9F20-4479-A899-59246E5CA766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
     <t>課題一覧</t>
     <rPh sb="0" eb="2">
@@ -220,16 +220,83 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームモード実装(やる気次第)
+操作方法などの資料の最終ページにアクセスコードを同封
+指定されたボタンを押して、コードを入力するとゲームが解放される
+解放状況はsettingsで管理</t>
+    <rPh sb="6" eb="8">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シダイ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>ソウサホウホウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ドウフウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>カイホウ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>カイホウ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>訂正モードの実装
-時間があれば</t>
+モード切り替え（改修）
+学習日はヘッダーへ移動
+新規モード
+資格名のシートに今日の日付のデータがあったらNG
+学習日は今日の日付で固定
+訂正モード（ラジオボタンで切り替え）
+資格名と学習日でシートとデータを検索
+行インデックスを記録
+この時、全ての項目を引用表示すること
+同じ日付の学習日がなければ新規と同じ
+更新時はその行の値を変更する
+同じ学習日がなければ新規と同じ動きをしたあと、日付でソートする</t>
     <rPh sb="0" eb="2">
       <t>テイセイ</t>
     </rPh>
     <rPh sb="6" eb="8">
       <t>ジッソウ</t>
     </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジカン</t>
+    <rPh sb="94" eb="95">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -269,7 +336,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -277,35 +344,389 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="9">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="47" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -321,14 +742,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}" name="テーブル1" displayName="テーブル1" ref="B5:F15" totalsRowShown="0">
-  <autoFilter ref="B5:F15" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}" name="テーブル1" displayName="テーブル1" ref="B5:F16" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+  <autoFilter ref="B5:F16" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}"/>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{A1D0E563-6C65-4A27-9D8B-5EE342B7CB85}" name="工程"/>
-    <tableColumn id="3" xr3:uid="{D6C44085-30F4-400F-835B-6B497DB97442}" name="対応内容"/>
-    <tableColumn id="1" xr3:uid="{98C22C1C-0394-4AD9-9ED9-DD8D31B7D7F1}" name="起票日"/>
-    <tableColumn id="5" xr3:uid="{4A6A6C10-F0C5-4115-B0A4-8290DBEA3D23}" name="実績日"/>
-    <tableColumn id="4" xr3:uid="{2F14591D-3E7E-427C-B7E1-2E41618E6342}" name="期限" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{A1D0E563-6C65-4A27-9D8B-5EE342B7CB85}" name="工程" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{D6C44085-30F4-400F-835B-6B497DB97442}" name="対応内容" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{98C22C1C-0394-4AD9-9ED9-DD8D31B7D7F1}" name="起票日" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{4A6A6C10-F0C5-4115-B0A4-8290DBEA3D23}" name="実績日" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{2F14591D-3E7E-427C-B7E1-2E41618E6342}" name="期限" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -651,11 +1072,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F429D69-C828-4F44-A95A-41969681F165}">
-  <dimension ref="B3:F15"/>
+  <dimension ref="B3:F16"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="3" max="3" width="48.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="8.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.25" bestFit="1" customWidth="1"/>
   </cols>
@@ -665,174 +1086,194 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B5" t="s">
+    <row r="4" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="5" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="20" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="16">
         <v>46158</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="16">
         <v>46171</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="17">
         <v>46173</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="5">
         <v>46158</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="5">
         <v>46158</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="6">
         <v>46173</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="9">
         <v>46158</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4">
+      <c r="E8" s="9"/>
+      <c r="F8" s="10">
         <v>46173</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="5">
         <v>46158</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="5">
         <v>46172</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="6">
         <v>46186</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="5">
         <v>46158</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="5">
         <v>46172</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="6">
         <v>46201</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B11" t="s">
+    <row r="11" spans="2:6" ht="393.75" x14ac:dyDescent="0.4">
+      <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="C11" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="5">
         <v>46172</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1">
+      <c r="E11" s="5"/>
+      <c r="F11" s="6">
         <v>46201</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="5">
         <v>46171</v>
       </c>
-      <c r="F12" s="1">
+      <c r="E12" s="4"/>
+      <c r="F12" s="6">
         <v>46201</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B13" t="s">
+    <row r="13" spans="2:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="B13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="5">
+        <v>46174</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C14" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D14" s="5">
         <v>46158</v>
       </c>
-      <c r="F13" s="1">
+      <c r="E14" s="4"/>
+      <c r="F14" s="6">
         <v>46214</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="1">
-        <v>46158</v>
-      </c>
-      <c r="F14" s="1">
-        <v>46264</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="5">
+        <v>46158</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="6">
+        <v>46264</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D16" s="14">
         <v>46158</v>
       </c>
-      <c r="F15" s="1">
+      <c r="E16" s="13"/>
+      <c r="F16" s="15">
         <v>46292</v>
       </c>
     </row>

--- a/Document/課題一覧表.xlsx
+++ b/Document/課題一覧表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7D9379-9F20-4479-A899-59246E5CA766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE6FE7B-CB48-4199-B34D-A801B8A07E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
   </bookViews>
@@ -273,7 +273,16 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>訂正モードの実装
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">訂正モードの実装
 モード切り替え（改修）
 学習日はヘッダーへ移動
 新規モード
@@ -284,8 +293,33 @@
 行インデックスを記録
 この時、全ての項目を引用表示すること
 同じ日付の学習日がなければ新規と同じ
-更新時はその行の値を変更する
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>更新時はその行の値を変更する
 同じ学習日がなければ新規と同じ動きをしたあと、日付でソートする</t>
+    </r>
     <rPh sb="0" eb="2">
       <t>テイセイ</t>
     </rPh>
@@ -305,7 +339,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,6 +352,31 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.499984740745262"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -506,7 +565,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -569,35 +628,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <numFmt numFmtId="47" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -726,6 +765,29 @@
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal/>
       </border>
     </dxf>
   </dxfs>
@@ -742,14 +804,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}" name="テーブル1" displayName="テーブル1" ref="B5:F16" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}" name="テーブル1" displayName="テーブル1" ref="B5:F16" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="B5:F16" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}"/>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{A1D0E563-6C65-4A27-9D8B-5EE342B7CB85}" name="工程" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{D6C44085-30F4-400F-835B-6B497DB97442}" name="対応内容" dataDxfId="5"/>
-    <tableColumn id="1" xr3:uid="{98C22C1C-0394-4AD9-9ED9-DD8D31B7D7F1}" name="起票日" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{4A6A6C10-F0C5-4115-B0A4-8290DBEA3D23}" name="実績日" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{2F14591D-3E7E-427C-B7E1-2E41618E6342}" name="期限" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{A1D0E563-6C65-4A27-9D8B-5EE342B7CB85}" name="工程" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{D6C44085-30F4-400F-835B-6B497DB97442}" name="対応内容" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{98C22C1C-0394-4AD9-9ED9-DD8D31B7D7F1}" name="起票日" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{4A6A6C10-F0C5-4115-B0A4-8290DBEA3D23}" name="実績日" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{2F14591D-3E7E-427C-B7E1-2E41618E6342}" name="期限" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1187,11 +1249,11 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="393.75" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="390.75" x14ac:dyDescent="0.4">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="21" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="5">
@@ -1212,7 +1274,9 @@
       <c r="D12" s="5">
         <v>46171</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="5">
+        <v>46206</v>
+      </c>
       <c r="F12" s="6">
         <v>46201</v>
       </c>

--- a/Document/課題一覧表.xlsx
+++ b/Document/課題一覧表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE6FE7B-CB48-4199-B34D-A801B8A07E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1802C75-DF24-43AD-81B4-A46784C98842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
+    <workbookView xWindow="4395" yWindow="4290" windowWidth="28800" windowHeight="15345" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
   </bookViews>
   <sheets>
     <sheet name="課題一覧" sheetId="1" r:id="rId1"/>
@@ -273,16 +273,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="2" tint="-0.499984740745262"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">訂正モードの実装
+    <t>訂正モードの実装
 モード切り替え（改修）
 学習日はヘッダーへ移動
 新規モード
@@ -293,33 +284,8 @@
 行インデックスを記録
 この時、全ての項目を引用表示すること
 同じ日付の学習日がなければ新規と同じ
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>更新時はその行の値を変更する
+更新時はその行の値を変更する
 同じ学習日がなければ新規と同じ動きをしたあと、日付でソートする</t>
-    </r>
     <rPh sb="0" eb="2">
       <t>テイセイ</t>
     </rPh>
@@ -339,7 +305,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,23 +318,6 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="2" tint="-0.499984740745262"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -629,7 +578,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1249,7 +1198,7 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="390.75" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="393.75" x14ac:dyDescent="0.4">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
@@ -1259,7 +1208,9 @@
       <c r="D11" s="5">
         <v>46172</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="5">
+        <v>46206</v>
+      </c>
       <c r="F11" s="6">
         <v>46201</v>
       </c>

--- a/Document/課題一覧表.xlsx
+++ b/Document/課題一覧表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1802C75-DF24-43AD-81B4-A46784C98842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E262B555-D635-4CB3-8EB4-54C640914A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4395" yWindow="4290" windowWidth="28800" windowHeight="15345" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
   </bookViews>
   <sheets>
     <sheet name="課題一覧" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
   <si>
     <t>課題一覧</t>
     <rPh sb="0" eb="2">
@@ -297,6 +297,33 @@
     </rPh>
     <rPh sb="96" eb="97">
       <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログ出力処理の整理(時間があれば)
+→画面のOpenCloseしか無い
+ドキュメントコメントの整理</t>
+    <rPh sb="2" eb="4">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>セイリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -753,8 +780,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}" name="テーブル1" displayName="テーブル1" ref="B5:F16" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="B5:F16" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}" name="テーブル1" displayName="テーブル1" ref="B5:F17" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="B5:F17" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}"/>
   <tableColumns count="5">
     <tableColumn id="2" xr3:uid="{A1D0E563-6C65-4A27-9D8B-5EE342B7CB85}" name="工程" dataDxfId="4"/>
     <tableColumn id="3" xr3:uid="{D6C44085-30F4-400F-835B-6B497DB97442}" name="対応内容" dataDxfId="3"/>
@@ -1083,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F429D69-C828-4F44-A95A-41969681F165}">
-  <dimension ref="B3:F16"/>
+  <dimension ref="B3:F17"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
@@ -1232,63 +1259,78 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="93.75" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="75" x14ac:dyDescent="0.4">
       <c r="B13" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="5">
+        <v>46206</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="B14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D14" s="5">
         <v>46174</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="6" t="s">
+      <c r="E14" s="4"/>
+      <c r="F14" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B14" s="3" t="s">
+    <row r="15" spans="2:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>17</v>
-      </c>
-      <c r="D14" s="5">
-        <v>46158</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="6">
-        <v>46214</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="D15" s="5">
         <v>46158</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="6">
-        <v>46264</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="5">
+        <v>46158</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="6">
+        <v>46264</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D17" s="14">
         <v>46158</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="15">
+      <c r="E17" s="13"/>
+      <c r="F17" s="15">
         <v>46292</v>
       </c>
     </row>

--- a/Document/課題一覧表.xlsx
+++ b/Document/課題一覧表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E262B555-D635-4CB3-8EB4-54C640914A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E593BE-A222-48D8-879C-C2499E0B579A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
   </bookViews>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="6">
-        <v>46214</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="93.75" x14ac:dyDescent="0.4">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="6">
-        <v>46214</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">

--- a/Document/課題一覧表.xlsx
+++ b/Document/課題一覧表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E593BE-A222-48D8-879C-C2499E0B579A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9726311-A060-4A0C-ACB2-44D217833226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3320F610-FD3E-4C4D-8B21-1A69D2A6F6FA}"/>
   </bookViews>
   <sheets>
     <sheet name="課題一覧" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>課題一覧</t>
     <rPh sb="0" eb="2">
@@ -187,26 +187,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>動作確認・テスト実施
-余裕があるならテスト項目を作る</t>
-    <rPh sb="0" eb="4">
-      <t>ドウサカクニン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ヨユウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>カスタムコントロール非活性時の色</t>
     <rPh sb="10" eb="13">
       <t>ヒカッセイ</t>
@@ -216,59 +196,6 @@
     </rPh>
     <rPh sb="15" eb="16">
       <t>イロ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゲームモード実装(やる気次第)
-操作方法などの資料の最終ページにアクセスコードを同封
-指定されたボタンを押して、コードを入力するとゲームが解放される
-解放状況はsettingsで管理</t>
-    <rPh sb="6" eb="8">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シダイ</t>
-    </rPh>
-    <rPh sb="16" eb="20">
-      <t>ソウサホウホウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>シリョウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>サイシュウ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>ドウフウ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="69" eb="71">
-      <t>カイホウ</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>カイホウ</t>
-    </rPh>
-    <rPh sb="77" eb="79">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="89" eb="91">
-      <t>カンリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -301,29 +228,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ログ出力処理の整理(時間があれば)
-→画面のOpenCloseしか無い
-ドキュメントコメントの整理</t>
-    <rPh sb="2" eb="4">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>セイリ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>セイリ</t>
+    <t>動作確認</t>
+    <rPh sb="0" eb="4">
+      <t>ドウサカクニン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -780,8 +687,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}" name="テーブル1" displayName="テーブル1" ref="B5:F17" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="B5:F17" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}" name="テーブル1" displayName="テーブル1" ref="B5:F15" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="B5:F15" xr:uid="{E547CE3F-92FA-459F-A87B-EE97EFBC616A}"/>
   <tableColumns count="5">
     <tableColumn id="2" xr3:uid="{A1D0E563-6C65-4A27-9D8B-5EE342B7CB85}" name="工程" dataDxfId="4"/>
     <tableColumn id="3" xr3:uid="{D6C44085-30F4-400F-835B-6B497DB97442}" name="対応内容" dataDxfId="3"/>
@@ -1110,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F429D69-C828-4F44-A95A-41969681F165}">
-  <dimension ref="B3:F17"/>
+  <dimension ref="B3:F15"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.375" customWidth="1"/>
@@ -1230,7 +1137,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D11" s="5">
         <v>46172</v>
@@ -1247,7 +1154,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" s="5">
         <v>46171</v>
@@ -1259,78 +1166,52 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="75" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D13" s="5">
+        <v>46158</v>
+      </c>
+      <c r="E13" s="5">
         <v>46206</v>
       </c>
-      <c r="E13" s="5"/>
       <c r="F13" s="6">
         <v>46230</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="93.75" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="D14" s="5">
-        <v>46174</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="6" t="s">
-        <v>19</v>
+        <v>46158</v>
+      </c>
+      <c r="E14" s="5">
+        <v>46256</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46264</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="5">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="14">
         <v>46158</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="6">
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="5">
-        <v>46158</v>
-      </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="6">
-        <v>46264</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B17" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="14">
-        <v>46158</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="15">
+      <c r="E15" s="13"/>
+      <c r="F15" s="15">
         <v>46292</v>
       </c>
     </row>
